--- a/data/trans_orig/P25D_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P25D_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la forma de consumir tabaco no tradicional  (se incluyen pipas de agua, cachimbas, vapeadores, cigarrillos electrónicos) en 2023</t>
+          <t>Población según la forma de consumir tabaco no tradicional  (se incluyen pipas de agua, cachimbas, vapeadores, cigarrillos electrónicos) en 2023 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10306</t>
+          <t>10548</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>923</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5538</t>
+          <t>5700</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2924</t>
+          <t>2844</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14430</t>
+          <t>13077</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10253</t>
+          <t>10833</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>877</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11049</t>
+          <t>10085</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13907</t>
+          <t>13747</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -956,97 +956,97 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1801</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>1837</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>442</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2386</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>442</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>2199</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13581</t>
+          <t>13775</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2921</t>
+          <t>2334</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>13706</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>528</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28062</t>
+          <t>31022</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>357</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31427</t>
+          <t>31361</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>272919</t>
+          <t>270535</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>302168</t>
+          <t>302099</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>276218</t>
+          <t>276201</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>286127</t>
+          <t>286122</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>555219</t>
+          <t>556157</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>586396</t>
+          <t>586781</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,62%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5490</t>
+          <t>5689</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32791</t>
+          <t>33594</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6202</t>
+          <t>6185</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23700</t>
+          <t>24428</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15467</t>
+          <t>16040</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>47070</t>
+          <t>48097</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10900</t>
+          <t>11512</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34291</t>
+          <t>34984</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>1465</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10877</t>
+          <t>12898</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15064</t>
+          <t>14682</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>38692</t>
+          <t>39129</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3159</t>
+          <t>3693</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28683</t>
+          <t>27444</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>155</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10082</t>
+          <t>7242</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>5349</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30726</t>
+          <t>30362</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2861</t>
+          <t>2868</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27311</t>
+          <t>26244</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6776</t>
+          <t>6961</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>4379</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>29912</t>
+          <t>28291</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31467</t>
+          <t>30955</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4124</t>
+          <t>4469</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>35231</t>
+          <t>31277</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>427011</t>
+          <t>426458</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>474743</t>
+          <t>473181</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>480606</t>
+          <t>480297</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>501953</t>
+          <t>501908</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>915518</t>
+          <t>916416</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>968683</t>
+          <t>969380</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,81%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11410</t>
+          <t>12475</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>711</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7129</t>
+          <t>8027</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4387</t>
+          <t>4229</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15211</t>
+          <t>15992</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4517</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>639</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6481</t>
+          <t>5711</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8020</t>
+          <t>7773</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>983</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10344</t>
+          <t>11180</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>647</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6832</t>
+          <t>6644</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14273</t>
+          <t>14174</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7848</t>
+          <t>7891</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,62 +2694,62 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>1564</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>1248</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>8726</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>1564</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>7811</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -2772,97 +2772,97 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>1681</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2789</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>551</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2812</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>3106</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>551</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>2822</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>295276</t>
+          <t>294102</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>309735</t>
+          <t>309740</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>335247</t>
+          <t>334529</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>344320</t>
+          <t>344518</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>634624</t>
+          <t>634111</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>651467</t>
+          <t>651706</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,97%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3292</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21759</t>
+          <t>23602</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>5077</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>24093</t>
+          <t>23457</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10299</t>
+          <t>11420</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>36667</t>
+          <t>38036</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2428</t>
+          <t>2211</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13599</t>
+          <t>13157</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1610</t>
+          <t>1619</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10144</t>
+          <t>10021</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5685</t>
+          <t>5155</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>19603</t>
+          <t>18839</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>8320</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4320</t>
+          <t>5063</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>659</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>9589</t>
+          <t>8828</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14880</t>
+          <t>13142</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>148</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10087</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1586</t>
+          <t>1702</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>17675</t>
+          <t>16530</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12701</t>
+          <t>12569</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>155</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12746</t>
+          <t>12569</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1673</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>16564</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>275785</t>
+          <t>274865</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>299603</t>
+          <t>299964</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>436037</t>
+          <t>436799</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>463111</t>
+          <t>462970</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>723038</t>
+          <t>722750</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>759667</t>
+          <t>758399</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>17661</t>
+          <t>18244</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>32471</t>
+          <t>33865</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>35891</t>
+          <t>36361</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>51779</t>
+          <t>51529</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>57162</t>
+          <t>59035</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>79288</t>
+          <t>80335</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4877</t>
+          <t>4126</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>751</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5832</t>
+          <t>5940</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7607</t>
+          <t>7970</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3412</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>426</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>3942</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>815</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5172</t>
+          <t>5641</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3375</t>
+          <t>3394</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>4199</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>412</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>5049</t>
+          <t>5177</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -4362,97 +4362,97 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>1225</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>2089</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="R36" s="2" t="inlineStr">
         <is>
           <t>363</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="S36" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>2131</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>2146</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>363</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>1797</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -4475,12 +4475,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>143176</t>
+          <t>141866</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>158781</t>
+          <t>157991</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>151548</t>
+          <t>151847</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>167884</t>
+          <t>167731</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>298979</t>
+          <t>299129</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>321990</t>
+          <t>321545</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,0%</t>
         </is>
       </c>
     </row>
@@ -4705,12 +4705,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>6365</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>23759</t>
+          <t>23676</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4720,12 +4720,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>10081</t>
+          <t>9727</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>9675</t>
+          <t>9725</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>28137</t>
+          <t>28220</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -4823,7 +4823,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>4421</t>
+          <t>4486</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>526</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>5124</t>
+          <t>5098</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>619</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>6705</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -4931,97 +4931,97 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>1798</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>1391</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>6995</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>2,72%</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K41" s="2" t="inlineStr">
+      <c r="R41" s="2" t="inlineStr">
         <is>
           <t>1798</t>
         </is>
       </c>
-      <c r="L41" s="2" t="inlineStr">
+      <c r="S41" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>7248</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>7161</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>1798</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>6290</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -5049,7 +5049,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>4370</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>4533</t>
+          <t>4881</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>6048</t>
+          <t>6013</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -5157,97 +5157,97 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>1391</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
+      <c r="R43" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>1071</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>1216</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5270,12 +5270,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>245063</t>
+          <t>244536</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>262177</t>
+          <t>261787</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5285,12 +5285,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5305,12 +5305,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>241383</t>
+          <t>241639</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>252912</t>
+          <t>252721</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>491030</t>
+          <t>492366</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>511797</t>
+          <t>512027</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -5500,12 +5500,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>18666</t>
+          <t>19571</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>47915</t>
+          <t>48339</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5515,12 +5515,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5535,12 +5535,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>10550</t>
+          <t>10553</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>39692</t>
+          <t>41405</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5570,12 +5570,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>32520</t>
+          <t>33505</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>78194</t>
+          <t>79291</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -5613,12 +5613,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>9294</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>27807</t>
+          <t>25603</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5628,12 +5628,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>3784</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>17507</t>
+          <t>17643</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>15900</t>
+          <t>14137</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>39221</t>
+          <t>37948</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5698,12 +5698,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -5726,12 +5726,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>3805</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>15941</t>
+          <t>15772</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>2461</t>
+          <t>2235</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>17592</t>
+          <t>18137</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>8152</t>
+          <t>7875</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>26563</t>
+          <t>27766</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>3959</t>
+          <t>3363</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>27073</t>
+          <t>24556</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>1441</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>20072</t>
+          <t>17900</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>6907</t>
+          <t>6660</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>34342</t>
+          <t>33307</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -5952,12 +5952,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>4061</t>
+          <t>4057</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>31568</t>
+          <t>27734</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1167</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>17492</t>
+          <t>18053</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6022,12 +6022,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>7266</t>
+          <t>7133</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>38311</t>
+          <t>37491</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>515454</t>
+          <t>514774</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>558420</t>
+          <t>557817</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6080,12 +6080,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>761765</t>
+          <t>759570</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>817024</t>
+          <t>818169</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>1292446</t>
+          <t>1291167</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>1378132</t>
+          <t>1381308</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,66%</t>
         </is>
       </c>
     </row>
@@ -6295,12 +6295,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t>2924</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>19563</t>
+          <t>20106</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>7272</t>
+          <t>6686</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>20049</t>
+          <t>21023</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>10970</t>
+          <t>11443</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>33731</t>
+          <t>33853</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -6408,12 +6408,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>806</t>
+          <t>852</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>9550</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6428,7 +6428,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>5104</t>
+          <t>4496</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>32423</t>
+          <t>30439</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6458,12 +6458,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>7845</t>
+          <t>7524</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>33691</t>
+          <t>39720</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -6521,12 +6521,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>3814</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>23167</t>
+          <t>22290</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6536,44 +6536,44 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>6653</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>3331</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>13655</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>6653</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>3065</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t>13662</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="O55" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
           <t>1,9%</t>
@@ -6591,12 +6591,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>9472</t>
+          <t>9515</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>30901</t>
+          <t>29866</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>16468</t>
+          <t>16793</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6649,12 +6649,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6669,12 +6669,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>4232</t>
+          <t>4095</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>16378</t>
+          <t>17525</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>9183</t>
+          <t>9244</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>26434</t>
+          <t>27612</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -6747,12 +6747,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>1607</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>626299</t>
+          <t>620951</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>9559</t>
+          <t>8883</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>4971</t>
+          <t>4968</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>771010</t>
+          <t>771848</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>46,93%</t>
         </is>
       </c>
     </row>
@@ -6860,12 +6860,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>282039</t>
+          <t>288658</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>883446</t>
+          <t>883784</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6875,12 +6875,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6895,12 +6895,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>656345</t>
+          <t>656410</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>687155</t>
+          <t>688092</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>824840</t>
+          <t>825796</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>1559863</t>
+          <t>1558353</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,75%</t>
         </is>
       </c>
     </row>
@@ -7090,12 +7090,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>83247</t>
+          <t>81554</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>140157</t>
+          <t>141201</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7105,12 +7105,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7125,12 +7125,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>89667</t>
+          <t>90221</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>135696</t>
+          <t>137908</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>188496</t>
+          <t>187718</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>263382</t>
+          <t>261841</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -7203,12 +7203,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>36254</t>
+          <t>34956</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>71688</t>
+          <t>72530</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7218,12 +7218,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7238,12 +7238,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>28259</t>
+          <t>28501</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>61179</t>
+          <t>63309</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7253,47 +7253,47 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>92141</t>
+        </is>
+      </c>
+      <c r="S61" s="2" t="inlineStr">
+        <is>
+          <t>73000</t>
+        </is>
+      </c>
+      <c r="T61" s="2" t="inlineStr">
+        <is>
+          <t>118721</t>
+        </is>
+      </c>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
           <t>1,67%</t>
-        </is>
-      </c>
-      <c r="Q61" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="R61" s="2" t="inlineStr">
-        <is>
-          <t>92141</t>
-        </is>
-      </c>
-      <c r="S61" s="2" t="inlineStr">
-        <is>
-          <t>72536</t>
-        </is>
-      </c>
-      <c r="T61" s="2" t="inlineStr">
-        <is>
-          <t>119429</t>
-        </is>
-      </c>
-      <c r="U61" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="V61" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="W61" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -7316,12 +7316,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>23831</t>
+          <t>23553</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>57128</t>
+          <t>57918</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7331,12 +7331,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>15475</t>
+          <t>15300</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>35432</t>
+          <t>36286</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>44527</t>
+          <t>44134</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>82700</t>
+          <t>81536</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -7429,12 +7429,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>23296</t>
+          <t>24011</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>59954</t>
+          <t>60266</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>14046</t>
+          <t>14051</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>38530</t>
+          <t>37248</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7484,7 +7484,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7499,12 +7499,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>42992</t>
+          <t>44132</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>84690</t>
+          <t>88272</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -7542,12 +7542,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>28008</t>
+          <t>31103</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>1047477</t>
+          <t>1088058</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>8283</t>
+          <t>8357</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>29315</t>
+          <t>28950</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>45117</t>
+          <t>42891</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>1254547</t>
+          <t>1207587</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>16,99%</t>
         </is>
       </c>
     </row>
@@ -7655,12 +7655,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>2225465</t>
+          <t>2168112</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>3173963</t>
+          <t>3166776</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7690,12 +7690,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>3403309</t>
+          <t>3398691</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>3481354</t>
+          <t>3480319</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7705,12 +7705,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7725,12 +7725,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>5529591</t>
+          <t>5575882</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>6621651</t>
+          <t>6621270</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7740,12 +7740,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,18%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P25D_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P25D_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3760</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>918</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10548</t>
+          <t>10303</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2425</t>
+          <t>4042</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>9289</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>6185</t>
+          <t>7953</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2844</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13077</t>
+          <t>14269</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>1635</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10833</t>
+          <t>7935</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3558</t>
+          <t>2798</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>847</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10085</t>
+          <t>7032</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>5599</t>
+          <t>4433</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13747</t>
+          <t>11116</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>478</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1837</t>
+          <t>2726</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>478</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>3024</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>3660</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13775</t>
+          <t>9881</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>493</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2334</t>
+          <t>2813</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>4837</t>
+          <t>4153</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13706</t>
+          <t>10773</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>7534</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>1748</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31022</t>
+          <t>18614</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>7534</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>1754</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31361</t>
+          <t>19837</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>292968</t>
+          <t>302104</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>270535</t>
+          <t>290449</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>302099</t>
+          <t>309823</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>282704</t>
+          <t>308251</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>276201</t>
+          <t>301697</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>286122</t>
+          <t>311865</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>575671</t>
+          <t>610355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>556157</t>
+          <t>598030</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>586781</t>
+          <t>619539</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,17 +1438,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14889</t>
+          <t>13776</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5689</t>
+          <t>5381</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33594</t>
+          <t>29352</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12121</t>
+          <t>13427</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6185</t>
+          <t>7123</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24428</t>
+          <t>25962</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>27010</t>
+          <t>27203</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16040</t>
+          <t>16096</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>48097</t>
+          <t>44569</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20101</t>
+          <t>22111</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11512</t>
+          <t>13299</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34984</t>
+          <t>34326</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4416</t>
+          <t>4382</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1465</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12898</t>
+          <t>12590</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>24517</t>
+          <t>26493</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14682</t>
+          <t>16263</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>39129</t>
+          <t>41508</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10951</t>
+          <t>11180</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3693</t>
+          <t>4166</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27444</t>
+          <t>27773</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>2549</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7242</t>
+          <t>9708</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>13729</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5349</t>
+          <t>5988</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30362</t>
+          <t>30786</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>11008</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>3983</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26244</t>
+          <t>27639</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>1683</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6961</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>11804</t>
+          <t>12692</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4379</t>
+          <t>4887</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28291</t>
+          <t>27081</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8478</t>
+          <t>6973</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1982,12 +1982,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>30955</t>
+          <t>22833</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4469</t>
+          <t>4459</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>9810</t>
+          <t>8305</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>31277</t>
+          <t>24884</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>453901</t>
+          <t>465599</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>426458</t>
+          <t>439879</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>473181</t>
+          <t>483923</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>493470</t>
+          <t>523120</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>480297</t>
+          <t>509567</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>501908</t>
+          <t>531744</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,27 +2155,27 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>947370</t>
+          <t>988719</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>916416</t>
+          <t>961175</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>969380</t>
+          <t>1010421</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,17 +2233,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2315,22 +2315,22 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5685</t>
+          <t>5580</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12475</t>
+          <t>12389</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>2808</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>626</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>6844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>8487</t>
+          <t>8388</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4229</t>
+          <t>3926</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15992</t>
+          <t>14721</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>2256</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4525</t>
+          <t>8789</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2614</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>694</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5711</t>
+          <t>6617</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7773</t>
+          <t>11854</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -2541,22 +2541,22 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3917</t>
+          <t>3786</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>978</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11180</t>
+          <t>11521</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,17 +2576,17 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2565</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>663</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6644</t>
+          <t>6422</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>6483</t>
+          <t>6391</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>2872</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14174</t>
+          <t>13009</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1564</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7891</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1564</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
@@ -2734,12 +2734,12 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>8726</t>
+          <t>8072</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>556</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2789</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>556</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -2880,32 +2880,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>303954</t>
+          <t>302922</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>294102</t>
+          <t>291596</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>309740</t>
+          <t>309280</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,32 +2915,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>340621</t>
+          <t>347798</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>334529</t>
+          <t>342479</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>344518</t>
+          <t>351605</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>644575</t>
+          <t>650721</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>634111</t>
+          <t>639973</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>651706</t>
+          <t>658582</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -2993,17 +2993,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,17 +3028,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>9348</t>
+          <t>10015</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3292</t>
+          <t>3365</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23602</t>
+          <t>23383</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>11313</t>
+          <t>12063</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>6157</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23457</t>
+          <t>26809</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>20661</t>
+          <t>22078</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11420</t>
+          <t>11159</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>38036</t>
+          <t>39441</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>6381</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t>2289</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13157</t>
+          <t>13621</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>4716</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1619</t>
+          <t>2136</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10021</t>
+          <t>10410</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>10898</t>
+          <t>11420</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5155</t>
+          <t>6469</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>18839</t>
+          <t>19424</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>4997</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3346,12 +3346,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8320</t>
+          <t>18934</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5063</t>
+          <t>3952</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2927</t>
+          <t>6288</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>8828</t>
+          <t>21841</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2545</t>
+          <t>2792</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3459,12 +3459,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13142</t>
+          <t>15291</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3484,32 +3484,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>13763</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,22 +3519,22 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>5762</t>
+          <t>7722</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1702</t>
+          <t>1744</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>16530</t>
+          <t>19694</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -3562,7 +3562,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2499</t>
+          <t>2775</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -3572,12 +3572,12 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12569</t>
+          <t>14588</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>4038</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>658</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12569</t>
+          <t>12179</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,22 +3632,22 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5813</t>
+          <t>6813</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1673</t>
+          <t>1695</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>16564</t>
+          <t>17833</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -3675,32 +3675,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>290352</t>
+          <t>346185</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>274865</t>
+          <t>327838</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>299964</t>
+          <t>358230</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,32 +3710,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>451862</t>
+          <t>394600</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>436799</t>
+          <t>379335</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>462970</t>
+          <t>403541</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>742213</t>
+          <t>740786</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>722750</t>
+          <t>719882</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>758399</t>
+          <t>758124</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>95,35%</t>
         </is>
       </c>
     </row>
@@ -3788,17 +3788,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>25083</t>
+          <t>28476</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>18244</t>
+          <t>20635</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>33865</t>
+          <t>37620</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>42975</t>
+          <t>47777</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>36361</t>
+          <t>39742</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>51529</t>
+          <t>56892</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>68058</t>
+          <t>76253</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>59035</t>
+          <t>63995</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>80335</t>
+          <t>89613</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,7%</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1479</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -4028,12 +4028,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>2269</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>763</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5940</t>
+          <t>6682</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>3456</t>
+          <t>3748</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7970</t>
+          <t>7979</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>780</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3923</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4166,32 +4166,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1603</t>
+          <t>1667</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>422</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3942</t>
+          <t>3823</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>2296</t>
+          <t>2447</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>807</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5641</t>
+          <t>5517</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>742</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3394</t>
+          <t>3767</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3840</t>
+          <t>4404</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,22 +4314,22 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>468</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>5177</t>
+          <t>5651</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>386</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>2214</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>386</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2146</t>
+          <t>2279</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -4470,32 +4470,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>150930</t>
+          <t>174188</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>141866</t>
+          <t>163956</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>157991</t>
+          <t>182217</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4505,32 +4505,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>160492</t>
+          <t>173906</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>151847</t>
+          <t>165229</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>167731</t>
+          <t>182810</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>311421</t>
+          <t>348093</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>299129</t>
+          <t>335289</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>321545</t>
+          <t>361529</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>83,52%</t>
         </is>
       </c>
     </row>
@@ -4583,17 +4583,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4618,17 +4618,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4653,17 +4653,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4700,32 +4700,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>12595</t>
+          <t>12154</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>6365</t>
+          <t>6635</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>23676</t>
+          <t>21973</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4735,32 +4735,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>4305</t>
+          <t>4238</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>9727</t>
+          <t>10435</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4770,32 +4770,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>16899</t>
+          <t>16393</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>9725</t>
+          <t>10047</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>28220</t>
+          <t>27729</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -4813,7 +4813,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>878</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>4486</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4848,22 +4848,22 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>528</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>5098</t>
+          <t>4858</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4883,22 +4883,22 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>661</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>7083</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -4961,7 +4961,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>1798</t>
+          <t>1789</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>6995</t>
+          <t>6560</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>1798</t>
+          <t>1789</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>6447</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>828</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -5049,7 +5049,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>4237</t>
+          <t>4592</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>849</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>4881</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>1720</t>
+          <t>1677</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>6013</t>
+          <t>6355</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -5265,32 +5265,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>255311</t>
+          <t>256847</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>244536</t>
+          <t>247453</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>261787</t>
+          <t>262952</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5300,32 +5300,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>248252</t>
+          <t>255084</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>241639</t>
+          <t>247880</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>252721</t>
+          <t>259422</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5335,32 +5335,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>503563</t>
+          <t>511931</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>492366</t>
+          <t>500438</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>512027</t>
+          <t>519922</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -5378,17 +5378,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5413,17 +5413,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5448,17 +5448,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5495,22 +5495,22 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>30936</t>
+          <t>34551</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>19571</t>
+          <t>22546</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>48339</t>
+          <t>53596</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5530,32 +5530,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>24701</t>
+          <t>26888</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>10553</t>
+          <t>17434</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>41405</t>
+          <t>40142</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5565,32 +5565,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>55637</t>
+          <t>61440</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>33505</t>
+          <t>45471</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>79291</t>
+          <t>82295</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -5608,32 +5608,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>15823</t>
+          <t>21093</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>13052</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>25603</t>
+          <t>35080</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5643,32 +5643,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>9869</t>
+          <t>11171</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>6126</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>17643</t>
+          <t>19698</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5678,32 +5678,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>25692</t>
+          <t>32264</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>14137</t>
+          <t>22620</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>37948</t>
+          <t>49331</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -5721,32 +5721,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>8444</t>
+          <t>8714</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>15772</t>
+          <t>16298</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5756,32 +5756,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>7487</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>2235</t>
+          <t>4153</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>18137</t>
+          <t>18238</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5791,32 +5791,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>15931</t>
+          <t>16924</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>7875</t>
+          <t>9338</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>27766</t>
+          <t>27779</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -5834,32 +5834,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>9420</t>
+          <t>14257</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>6635</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>24556</t>
+          <t>30902</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5869,32 +5869,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>7144</t>
+          <t>7775</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>1441</t>
+          <t>2435</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>17900</t>
+          <t>19534</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5904,32 +5904,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>16565</t>
+          <t>22032</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>6660</t>
+          <t>11812</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>33307</t>
+          <t>38780</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -5947,32 +5947,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>12370</t>
+          <t>11725</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>27734</t>
+          <t>27535</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5982,32 +5982,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>5953</t>
+          <t>9308</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>1167</t>
+          <t>3354</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>18053</t>
+          <t>22295</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6017,32 +6017,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>18323</t>
+          <t>21032</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>7133</t>
+          <t>10736</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>37491</t>
+          <t>40482</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -6060,102 +6060,102 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>539582</t>
+          <t>620496</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>514774</t>
+          <t>592743</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>557817</t>
+          <t>639340</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
+          <t>87,29%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>83,39%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>89,94%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>701522</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>682904</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>716941</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>91,72%</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>89,28%</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>93,73%</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>1416</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>1322019</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>1291332</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>1349416</t>
+        </is>
+      </c>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>89,59%</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
           <t>87,51%</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>83,49%</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>90,47%</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>890</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>787463</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>759570</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>818169</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>93,45%</t>
-        </is>
-      </c>
-      <c r="O51" s="2" t="inlineStr">
-        <is>
-          <t>90,14%</t>
-        </is>
-      </c>
-      <c r="P51" s="2" t="inlineStr">
-        <is>
-          <t>97,1%</t>
-        </is>
-      </c>
-      <c r="Q51" s="2" t="inlineStr">
-        <is>
-          <t>1416</t>
-        </is>
-      </c>
-      <c r="R51" s="2" t="inlineStr">
-        <is>
-          <t>1327045</t>
-        </is>
-      </c>
-      <c r="S51" s="2" t="inlineStr">
-        <is>
-          <t>1291167</t>
-        </is>
-      </c>
-      <c r="T51" s="2" t="inlineStr">
-        <is>
-          <t>1381308</t>
-        </is>
-      </c>
-      <c r="U51" s="2" t="inlineStr">
-        <is>
-          <t>90,94%</t>
-        </is>
-      </c>
-      <c r="V51" s="2" t="inlineStr">
-        <is>
-          <t>88,49%</t>
-        </is>
-      </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>91,44%</t>
         </is>
       </c>
     </row>
@@ -6173,17 +6173,17 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>616575</t>
+          <t>710836</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>616575</t>
+          <t>710836</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>616575</t>
+          <t>710836</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6208,17 +6208,17 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>842617</t>
+          <t>764875</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>842617</t>
+          <t>764875</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>842617</t>
+          <t>764875</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6243,17 +6243,17 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>1459192</t>
+          <t>1475711</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>1459192</t>
+          <t>1475711</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>1459192</t>
+          <t>1475711</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6290,32 +6290,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>8880</t>
+          <t>10800</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>2924</t>
+          <t>4601</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>20106</t>
+          <t>21551</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6325,32 +6325,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>12437</t>
+          <t>14336</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>6686</t>
+          <t>8535</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>21023</t>
+          <t>25292</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6360,32 +6360,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>21317</t>
+          <t>25136</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>11443</t>
+          <t>15314</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>33853</t>
+          <t>39037</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -6403,32 +6403,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>4058</t>
+          <t>4476</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>10719</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6438,32 +6438,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>11692</t>
+          <t>7596</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>4496</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>30439</t>
+          <t>12936</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6473,32 +6473,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>15749</t>
+          <t>12072</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>7524</t>
+          <t>6743</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>39720</t>
+          <t>19677</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -6516,32 +6516,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>11774</t>
+          <t>13149</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>3814</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>22290</t>
+          <t>22187</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6551,32 +6551,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>6653</t>
+          <t>7355</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>3331</t>
+          <t>2909</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>13655</t>
+          <t>13791</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6586,32 +6586,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>18427</t>
+          <t>20504</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>9515</t>
+          <t>11920</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>29866</t>
+          <t>32619</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -6629,32 +6629,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>8658</t>
+          <t>10058</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>2898</t>
+          <t>4486</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>16793</t>
+          <t>18010</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6664,32 +6664,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>8241</t>
+          <t>9344</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>4095</t>
+          <t>4985</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>17525</t>
+          <t>20438</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6699,32 +6699,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>16899</t>
+          <t>19402</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>9244</t>
+          <t>11920</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>27612</t>
+          <t>31234</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -6742,32 +6742,32 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>246541</t>
+          <t>3288</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>1607</t>
+          <t>862</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>620951</t>
+          <t>9096</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6777,32 +6777,32 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>3678</t>
+          <t>4103</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>8883</t>
+          <t>9754</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6812,32 +6812,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>250218</t>
+          <t>7391</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>4968</t>
+          <t>3403</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>771848</t>
+          <t>13845</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -6855,32 +6855,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>646996</t>
+          <t>754352</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>288658</t>
+          <t>739743</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>883784</t>
+          <t>766754</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6890,32 +6890,32 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>675031</t>
+          <t>788598</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>656410</t>
+          <t>773163</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>688092</t>
+          <t>798951</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6925,32 +6925,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>1322028</t>
+          <t>1542950</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>825796</t>
+          <t>1521543</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>1558353</t>
+          <t>1558740</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>95,78%</t>
         </is>
       </c>
     </row>
@@ -6968,17 +6968,17 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>926906</t>
+          <t>796123</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>926906</t>
+          <t>796123</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>926906</t>
+          <t>796123</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7003,17 +7003,17 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7038,17 +7038,17 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>1644638</t>
+          <t>1627455</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>1644638</t>
+          <t>1627455</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>1644638</t>
+          <t>1627455</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7085,32 +7085,32 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>111174</t>
+          <t>119264</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>81554</t>
+          <t>96483</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>141201</t>
+          <t>147680</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7120,32 +7120,32 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>113078</t>
+          <t>125579</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>90221</t>
+          <t>105367</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>137908</t>
+          <t>149934</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7155,32 +7155,32 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>224253</t>
+          <t>244844</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>187718</t>
+          <t>211190</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>261841</t>
+          <t>276669</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -7198,67 +7198,67 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>51381</t>
+          <t>60309</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>34956</t>
+          <t>44817</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>72530</t>
+          <t>81034</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>37660</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>27356</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>48890</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
           <t>1,01%</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>40760</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>28501</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr">
-        <is>
-          <t>63309</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7268,27 +7268,27 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>92141</t>
+          <t>97968</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>73000</t>
+          <t>80404</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>118721</t>
+          <t>120988</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7311,32 +7311,32 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>37411</t>
+          <t>42606</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>23553</t>
+          <t>28507</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>57918</t>
+          <t>62490</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7346,32 +7346,32 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>23740</t>
+          <t>25944</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>15300</t>
+          <t>17746</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>36286</t>
+          <t>39041</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7381,32 +7381,32 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>61151</t>
+          <t>68550</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>44134</t>
+          <t>50758</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>81536</t>
+          <t>92172</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -7424,32 +7424,32 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>38109</t>
+          <t>44793</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>24011</t>
+          <t>29843</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>60266</t>
+          <t>68914</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7459,32 +7459,32 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>22845</t>
+          <t>26285</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>14051</t>
+          <t>16408</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>37248</t>
+          <t>39993</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7494,32 +7494,32 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>60953</t>
+          <t>71078</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>44132</t>
+          <t>51980</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>88272</t>
+          <t>93838</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -7537,69 +7537,69 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>278232</t>
+          <t>32294</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>31103</t>
+          <t>16765</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>1088058</t>
+          <t>57652</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>19723</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>11981</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>33565</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
           <t>0,9%</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>31,54%</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>15192</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t>8357</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr">
-        <is>
-          <t>28950</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="O64" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="P64" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
           <t>32</t>
@@ -7607,32 +7607,32 @@
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>293424</t>
+          <t>52017</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>42891</t>
+          <t>33514</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>1207587</t>
+          <t>78056</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -7650,32 +7650,32 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>2933993</t>
+          <t>3222696</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>2168112</t>
+          <t>3173821</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>3166776</t>
+          <t>3261218</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7685,32 +7685,32 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>3439894</t>
+          <t>3492880</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>3398691</t>
+          <t>3459627</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>3480319</t>
+          <t>3520318</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7720,32 +7720,32 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>6373886</t>
+          <t>6715575</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>5575882</t>
+          <t>6665986</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>6621270</t>
+          <t>6768208</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,35%</t>
         </is>
       </c>
     </row>
@@ -7763,17 +7763,17 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>3450299</t>
+          <t>3521963</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>3450299</t>
+          <t>3521963</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>3450299</t>
+          <t>3521963</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -7798,17 +7798,17 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>3655510</t>
+          <t>3728070</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>3655510</t>
+          <t>3728070</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>3655510</t>
+          <t>3728070</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -7833,17 +7833,17 @@
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>7105808</t>
+          <t>7250032</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>7105808</t>
+          <t>7250032</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>7105808</t>
+          <t>7250032</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
